--- a/原始資料/一梅花開叫.xlsx
+++ b/原始資料/一梅花開叫.xlsx
@@ -18,8 +18,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9.1♣–2♣ A–F分支" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10.1♣–2♦系統" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11.1♣–2♥系統" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.1♣–2♠系統" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.1♣–2NT系統" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12.(原)1♣–2♠系統" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.(原)1♣–2NT系統" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14.第十一章改動1" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,12 +102,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F5FA"/>
+        <fgColor rgb="00DCE6F1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCE6F1"/>
+        <fgColor rgb="00F2F5FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -221,6 +222,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -230,16 +240,7 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -610,7 +611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -646,374 +647,462 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>★ 家規點力</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>本檔採用家規點力：**所有開叫點力下修 1 點、所有答叫點力上修 1 點**（聯手總點力因此維持不變）。括號內或註明「原書」者為原書印行的數值。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>開叫定義</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>1♣ = 任何至少 16 點以上的牌。這是全體系唯一的強開叫。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>1♣ = 任何至少 15 點以上的牌（家規下修 1 點；原書 16 點以上）。這是全體系唯一的強開叫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>★ 方向相反</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>本章與第四、五章最大的不同：1♣ 是強牌，所以**描述牌型的是應叫者，接力發問的是開叫者**。第四、五章是開叫者描述、應叫者問——讀本章的表時務必注意主詞。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>點力階梯</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>1♣ – 1♦（0-7點）後：1♥ = 至少20點，其他再叫都是 16-19 點。
-1♣ – 1♦ – 1♥ 後：1♠ = 再度示弱（0-4點），其他叫品都顯示 5-7（8）點並建立逼叫進局形勢。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>為何 2♥ 是雙低花</t>
+          <t>點力階梯</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2♥ 應叫顯示低花 4-5 或 5-4、8+ 點。邏輯是節省低花積極應叫的空間——雙低花第二次再叫至少要到三階，會使後續接力設計十分倉促。</t>
+          <t>1♣ – 1♦（0-8點）後：1♥ = 至少19點，其他再叫都是 15-18 點。
+1♣ – 1♦ – 1♥ 後：1♠ = 再度示弱（0-5點），其他叫品都顯示 6-8（9）點並建立逼叫進局形勢。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>為何 2♥ 是雙低花</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2♥ 應叫顯示低花 4-5 或 5-4、9+ 點。邏輯是節省低花積極應叫的空間——雙低花第二次再叫至少要到三階，會使後續接力設計十分倉促。</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
           <t>牌型寫法</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>四位數字一律按 ♠-♥-♦-♣ 順序。例：2-2-2-7 是 7張♣。</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr"/>
-    </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr"/>
+      <c r="B11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>七套獨立的應叫體系</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>接力扳機</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>1♦（0-7點）</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>1♥（20+）或其他 16-19 點再叫 → 見表 3、4、5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>1NT（均型 8-14）</t>
+          <t>1♦（0-8點）</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2♣ 是接力扳機 → 見表 6、7</t>
+          <t>1♥（19+）或其他 15-18 點再叫 → 見表 3、4、5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2♣（5+♣，8+）</t>
+          <t>1NT（均型 9-15）</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>2♦ 是接力扳機 → 見表 8、9</t>
+          <t>2♣ 是接力扳機 → 見表 6、7</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2♦（5+♦，8+）</t>
+          <t>2♣（5+♣，9+）</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>2♥ 是接力扳機 → 見表 10</t>
+          <t>2♦ 是接力扳機 → 見表 8、9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>2♥（低花 5-4／4-5，8+）</t>
+          <t>2♦（5+♦，9+）</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>2♠ 是接力扳機 → 見表 11</t>
+          <t>2♥ 是接力扳機 → 見表 10</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>2♠（均型兩個4張套，15+）</t>
+          <t>2♥（低花 5-4／4-5，9+）</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>2NT 是接力扳機 → 見表 12</t>
+          <t>2♠ 是接力扳機 → 見表 11</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>2NT（均型一個4張套或5張低花，15+）</t>
+          <t>2♠（4441黑花單張，13+）★</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>3♣ 是接力扳機 → 見表 13</t>
+          <t>【第十一章改動1】原為「均型兩個4張套，16+」→ 原設計見表 12</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="5" t="inlineStr"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2NT（4441紅花單張，13+）★</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>【第十一章改動1】原為「均型一個4張套或5張低花，16+」→ 原設計見表 13</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>1♥（5+♥，9+　或　16+均型）★</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>【第十一章改動1】1♠ 是新的接力扳機；1NT 答叫 = 16+均型 → 轉入表 6、7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>本章需要留意的地方</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>說明</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>'54Pick-up 有兩種階梯</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>四級版：6-4、5422、5413、5431。
 五級版：6-4、5-5、5422、5413、5431。差別在 5-5 有沒有被先前的叫牌排除——這正是第三章講的「階梯塌縮」。</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>NT 階梯是在數點力</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>1♠ 示弱線底下那組 2NT/3NT/4NT/5NT（24-25／26-27／28-30／30-32 點）是在數聯手大牌點，與接力答叫無關，不要和階梯級數混淆。</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>「多加一級」的變體</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>多處註明「後續答叫的設計和上面的階梯一模一樣，只要多加一級即可」——即第一級用來表示 8-11 點的低限，其餘級數整體往上順延一級。</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>多處註明「後續答叫的設計和上面的階梯一模一樣，只要多加一級即可」——即第一級用來表示 9-12 點的低限，其餘級數整體往上順延一級。</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>工作表</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>內容</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>2. 對1♣的應叫</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>應叫者的全部第一應叫，含 3♣／3♦（4441）的子接力。</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>3. 1♦後開叫者再叫</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>1♣ – 1♦ 後開叫者描述自己 16-19 點牌型（此段是自然叫，非接力）。</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>4. 1♦–1♥後應叫者描述</t>
+          <t>2. 對1♣的應叫</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>開叫者顯示 20+ 後，應叫者的描述叫品與 NT 點力階梯。</t>
+          <t>應叫者的全部第一應叫，含 3♣／3♦（4441）的子接力。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>5. 1NT分支續問</t>
+          <t>3. 1♦後開叫者再叫</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>應叫者顯示 5 張♠套後的完整答叫階梯。</t>
+          <t>1♣ – 1♦ 後開叫者描述自己 15-18 點牌型（此段是自然叫，非接力）。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>6. 1♣–1NT 主幹</t>
+          <t>4. 1♦–1♥後應叫者描述</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>均型應叫後的第一次接力。</t>
+          <t>開叫者顯示 19+ 後，應叫者的描述叫品與 NT 點力階梯。</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>7. 1♣–1NT 第二次接力</t>
+          <t>5. 1NT分支續問</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>12-14 點後的 7 種再叫，含兩組巢狀子接力。</t>
+          <t>應叫者顯示 5 張♠套後的完整答叫階梯。</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>8. 1♣–2♣ 主幹</t>
+          <t>6. 1♣–1NT 主幹</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>5+♣ 應叫後的 11 種再叫。</t>
+          <t>均型應叫後的第一次接力。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>9. 1♣–2♣ A–F分支</t>
+          <t>7. 1♣–1NT 第二次接力</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>六個分支的第二次接力，合併於一表。</t>
+          <t>13-15 點後的 7 種再叫，含兩組巢狀子接力。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>10. 1♣–2♦ 系統</t>
+          <t>8. 1♣–2♣ 主幹</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>5+♦ 應叫後的 10 種再叫，加書中給的 A 分支範例。</t>
+          <t>5+♣ 應叫後的 11 種再叫。</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>11. 1♣–2♥ 系統</t>
+          <t>9. 1♣–2♣ A–F分支</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>雙低花應叫後的 4 種再叫。</t>
+          <t>六個分支的第二次接力，合併於一表。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>12. 1♣–2♠ 系統</t>
+          <t>10. 1♣–2♦ 系統</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>均型兩個4張套，含 A／B 的第二次接力。</t>
+          <t>5+♦ 應叫後的 10 種再叫，加書中給的 A 分支範例。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>13. 1♣–2NT 系統</t>
+          <t>11. 1♣–2♥ 系統</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>均型一個4張套或5張低花套的 6 種再叫。</t>
+          <t>雙低花應叫後的 4 種再叫。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>12. (原) 1♣–2♠ 系統</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>第十一章前的原設計：均型兩個4張套，含 A／B 的第二次接力。保留供對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>13. (原) 1♣–2NT 系統</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>第十一章前的原設計：均型一個4張套或5張低花套的 6 種再叫。保留供對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>14. 第十一章改動1</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>★ 1♥ 應叫雙重含義、1♠ 接力，以及騰出來的 2♠／2NT／3♥／3♠ 新舊對照。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>★ 第十一章改動1</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>改了什麼</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>1♣ – 1♥ 的 1♥ 應叫改為雙重含義：5張以上♥、9+點；或 16點以上均型牌。開叫者用 **1♠ 接力** 區分（1NT 答叫 = 16+均型，2♣ 答叫 = ♥套），而開叫者的 1NT 再叫則改為顯示♠套。</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>換來什麼</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>兩種均型強牌全部併進 1♥，空出 2♠／2NT 改給 13+ 點的 4441；原本的 3♠／3NT／4♣／4♦（4441、13+）一併取代，3♠ 改為「隨你定！」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>原設計去哪了</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>表 12、13 已改標「(原)」並保留，供對照與回溯。</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1140,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – 2♦ ； 2♥ – ？　（2♦ = 5張♦，8+大牌點。應叫者有 10 種可能的再叫）</t>
+          <t>1♣ – 2♦ ； 2♥ – ？　（2♦ = 5張♦，9+大牌點。應叫者有 10 種可能的再叫）</t>
         </is>
       </c>
     </row>
@@ -1117,27 +1206,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2NT</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>4張♥</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>'54Pick-up</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1163,27 +1252,27 @@
       <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>6張以上♦ + 4張♣</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>接力</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1193,7 +1282,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>7張♦，8-11大牌點</t>
+          <t>7張♦，9-12大牌點</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -1209,27 +1298,27 @@
       <c r="E9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>7321牌型，12+大牌點</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>7321牌型，13+大牌點</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Splinter接力</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -1239,7 +1328,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>2-2-7-2，12+大牌點</t>
+          <t>2-2-7-2，13+大牌點</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -1255,27 +1344,27 @@
       <c r="E11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>3-3-7-0，12+大牌點</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>3-3-7-0，13+大牌點</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1285,7 +1374,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>3-0-7-3，12+大牌點</t>
+          <t>3-0-7-3，13+大牌點</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1301,32 +1390,32 @@
       <c r="E13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>0-3-7-3，12+大牌點</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>0-3-7-3，13+大牌點</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>4♠</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="22" t="inlineStr">
         <is>
-          <t>【A分支】　1♣ – 2♦ ； 2♥ – 2♠ ； 2NT – ？　（2♠ = 4張♠；高於 3♦ 的應叫都表示 12+ 大牌點）　　書中說「後續叫牌和 1♣ – 2♣ 後極為相似，只給出一個例子」</t>
+          <t>【A分支】　1♣ – 2♦ ； 2♥ – 2♠ ； 2NT – ？　（2♠ = 4張♠；高於 3♦ 的應叫都表示 13+ 大牌點）　　書中說「後續叫牌和 1♣ – 2♣ 後極為相似，只給出一個例子」</t>
         </is>
       </c>
       <c r="B15" s="23" t="n"/>
@@ -1335,27 +1424,27 @@
       <c r="E15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>8-11大牌點</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>9-12大牌點</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>'54Pick-up　＊</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -1381,27 +1470,27 @@
       <c r="E17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>4-2-5-2，12+</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -1427,27 +1516,27 @@
       <c r="E19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>4-3-5-1，12+</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
@@ -1473,27 +1562,27 @@
       <c r="E21" s="11" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>4-0-5-4，12+</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="inlineStr"/>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
@@ -1578,7 +1667,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2♥ = 低花 5-4 或 4-5，8+大牌點。</t>
+          <t>2♥ = 低花 5-4 或 4-5，9+大牌點。</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1706,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>4張♦ + 5張♣，8-11大牌點</t>
+          <t>4張♦ + 5張♣，9-12大牌點</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -1633,27 +1722,27 @@
       <c r="E5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>5張♦ + 4張♣，8-11大牌點</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>5張♦ + 4張♣，9-12大牌點</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -1663,7 +1752,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4張♦ + 5張♣，12+大牌點</t>
+          <t>4張♦ + 5張♣，13+大牌點</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -1679,27 +1768,27 @@
       <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>5張♦ + 4張♣，12+大牌點</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>5張♦ + 4張♣，13+大牌點</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1746,21 +1835,21 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1♣ – 2♠ 後的接力叫牌</t>
+          <t>【第十一章前的原設計】1♣ – 2♠ 後的接力叫牌</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – 2♠ ； 2NT – ？　（應叫者有 6 種可能的再叫）</t>
+          <t>1♣ – 2♠ ； 2NT – ？　（應叫者有 6 種可能的再叫）　※ 第十一章改動1後 2♠ 已改為 4441（黑花單張，12+），本表僅供對照</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2♠ = 均型牌，有兩個4張套，15+大牌點。此後的接力和 1♣ – 2NT 後的叫牌都基於 Sidestep 原則。</t>
+          <t>（原）2♠ = 均型牌，有兩個4張套，16+大牌點。此後的接力和 1♣ – 2NT 後的叫牌都基於 Sidestep 原則。　★ 第十一章後，這種均型強牌改走 1♥ → 1♠ → 1NT，續叫沿用表 6、7（點力讀 16-17／18+）。</t>
         </is>
       </c>
     </row>
@@ -1819,27 +1908,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>B　3♦</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>黑花色4-4　或　紅花色4-4</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>接力</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>細分見下方</t>
         </is>
@@ -1869,27 +1958,27 @@
       <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>4-3-4-2</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -1915,27 +2004,27 @@
       <c r="E9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>4-4-3-2</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
@@ -1949,27 +2038,27 @@
       <c r="E11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>2-3-4-4，15+大牌點</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>2-3-4-4，16+大牌點</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -1979,7 +2068,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>3-2-4-4，15+大牌點</t>
+          <t>3-2-4-4，16+大牌點</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -1995,27 +2084,27 @@
       <c r="E13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>2-4-3-4，15+大牌點</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>2-4-3-4，16+大牌點</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -2025,7 +2114,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>3-4-2-4，15+大牌點</t>
+          <t>3-4-2-4，16+大牌點</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -2059,7 +2148,7 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>4-2-3-4，15+大牌點</t>
+          <t>4-2-3-4，16+大牌點</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
@@ -2075,27 +2164,27 @@
       <c r="E17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>4-3-2-4，15+大牌點</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>4-3-2-4，16+大牌點</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -2105,7 +2194,7 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>2-4-4-3，15+大牌點</t>
+          <t>2-4-4-3，16+大牌點</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -2121,27 +2210,27 @@
       <c r="E19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>3-4-4-2，15+大牌點</t>
-        </is>
-      </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>3-4-4-2，16+大牌點</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2153,7 +2242,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>注意檢查最後一章「最後的改動」是否修改了本節。</t>
+          <t>★ 已確認：第十一章改動1 取代了本節的 2♠ 含義，本表保留為原設計對照。新設計見表 14。</t>
         </is>
       </c>
     </row>
@@ -2190,21 +2279,21 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>1♣ – 2NT 後的接力叫牌</t>
+          <t>【第十一章前的原設計】1♣ – 2NT 後的接力叫牌</t>
         </is>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – 2NT ； 3♣ – ？　（應叫者有 6 種可能的再叫）</t>
+          <t>1♣ – 2NT ； 3♣ – ？　（應叫者有 6 種可能的再叫）　※ 第十一章改動1後 2NT 已改為 4441（紅花單張，12+），本表僅供對照</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2NT = 均型牌，帶一個花色不明的4張套或一個5張低花套，15+大牌點。</t>
+          <t>（原）2NT = 均型牌，帶一個花色不明的4張套或一個5張低花套，16+大牌點。　★ 第十一章後，這種均型強牌改走 1♥ → 1♠ → 1NT，續叫沿用表 6、7（點力讀 16-17／18+）。</t>
         </is>
       </c>
     </row>
@@ -2259,27 +2348,27 @@
       <c r="E5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>5332牌型，5張♦</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>Splinter接力</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -2305,27 +2394,27 @@
       <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>3-3-4-3（4張套是♦）</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E8" s="14" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -2351,27 +2440,27 @@
       <c r="E9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>4-3-3-3（4張套是♠）</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E10" s="14" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2385,6 +2474,340 @@
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A3:E3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>第十一章改動1：1♣ – 1♥ – 1♠ ＝ 接力</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>1♣ – 1♥ ； 1♠ – ？　（1♥ ＝ 5張以上♥、9個以上大牌點　或　16點以上均型牌）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="25" t="inlineStr">
+        <is>
+          <t>作者在與 Geir Helgemo 搭檔前重新評估體系，把強♣後的 1♥ 應叫賦予雙重含義，於是 1♠ 可以當接力叫，而開叫者的 1NT 再叫改為顯示♠套。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>應叫者叫品</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>含義</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>開叫者接力</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>接力類型</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>【一】1♠ 接力之後，應叫者的再叫</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>1NT</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>16點以上，均型牌。後續接力同 1♣ – 1NT，只是點力範圍改成 16-17點（低限）或 18點以上（高限）。</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>轉入表 6、7</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>點力刻度改讀</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>2♣</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t>表示持有♥套。後續叫牌原則上同 1♣ – 1♥ – 1NT。</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t>轉入第五章</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>【二】騰出來的空間：1♣ 開叫後的積極性應叫（新舊對照）</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="24" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2♠</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>新：4-4-4-1牌型，有一個黑花色單張，13個以上大牌點。</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>2NT</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>接力扳機</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>舊：均型牌，兩個4張套，16+點</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>2NT</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>新：4-4-4-1牌型，有一個紅花色單張，13個以上大牌點。</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>3♣</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>接力扳機</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>舊：均型牌，一個4張套或一個5張低花套，16+點</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>3♣</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>4-4-4-1牌型，有一個黑花色單張，9-13大牌點。（和前面設計一樣）</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>3♦</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>接力（Sidestep原則）</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>未變</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>3♦</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>4-4-4-1牌型，有一個紅花色單張，9-13大牌點。（和前面設計一樣）</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>3♥</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>接力</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>未變</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>3♥</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>一個堅固的7張套花色，邊花沒有牌力。</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>3♠／4♣</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>詢問／要求扣叫</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>加註「邊花沒有牌力」</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>3♠</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>隨你定！（例如可以是一個堅固的7張套花色，邊花還有牌力）</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>由搭檔自訂</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>舊：3♠／3NT／4♣／4♦ ＝ 4441，比應叫花色高一級的花色是單張，13+點</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>原書對照段落：「原本 2♠ ＝ 均型牌有兩個4張套、15+點；2NT ＝ 均型牌有一個4張套或一個5張低花套、15+點。這兩種均型強牌現在全部併進 1♥ 應叫（再用 1NT 表明），空出來的 2♠／2NT 改給 12+ 點的 4441。」（此段為原書原文點力；本檔表列數值已按家規：開叫 -1、答叫 +1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>表 12、13 保留了這兩個叫品的原設計（表名已加「(原)」），供對照與回溯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>書中未列出新的 2♠／2NT（4441、12+）之後的答叫階梯。可比照 3♣／3♦（4441、8-12）的子接力推想，但原書並未明文，本表不代為補寫。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2397,7 +2820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2417,7 +2840,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – ？　（1♣ = 任何至少16點以上的牌）</t>
+          <t>1♣ – ？　（1♣ = 任何至少15點以上的牌）</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2879,7 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>0-7（8）個大牌點，任何牌型。</t>
+          <t>0-8（9）個大牌點，任何牌型。</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -2478,423 +2901,520 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>1♥／1♠</t>
+          <t>▸ 1♥</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>5張以上套，至少8個大牌點。如果開叫者再叫 1NT，此後接力方式完全遵循 1♥／1♠ – 1NT 的設計（第五章）。其他叫牌都是自然的。</t>
+          <t>【第十一章改動1】雙重含義：5張以上♥、9個以上大牌點；**或** 16點以上的均型牌。</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
         <is>
+          <t>1♠</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>接力（新）</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>以下 2 列為 1♠ 接力後的再叫</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　1NT</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>16點以上，均型牌。後續接力同 1♣ – 1NT，只是點力範圍改成 16-17點（低限）／18點以上（高限）。</t>
+        </is>
+      </c>
+      <c r="C6" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
-        <is>
-          <t>積極應叫</t>
-        </is>
-      </c>
-      <c r="E5" s="14" t="inlineStr">
-        <is>
-          <t>見第五章</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>1NT</t>
-        </is>
-      </c>
-      <c r="B6" s="11" t="inlineStr">
-        <is>
-          <t>均型牌，8（9）-14個大牌點。</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>2♣</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="inlineStr">
-        <is>
-          <t>接力扳機</t>
-        </is>
-      </c>
-      <c r="E6" s="11" t="inlineStr">
-        <is>
-          <t>見表 6、7</t>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>轉入表 6、7</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>點力改讀 16-17／18+</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>2♣</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>至少5張♣和8個大牌點。但5332牌型帶一低花套通常被認為是均型牌。</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr">
-        <is>
-          <t>2♦</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>接力扳機</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>見表 8、9</t>
-        </is>
-      </c>
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　2♣</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>表示持有♥套。後續叫牌原則上同 1♣ – 1♥ – 1NT。</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>轉入第五章</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>2♦</t>
+          <t>1♠</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>至少5張♦和8個大牌點，其餘同 2♣。</t>
+          <t>5張以上♠，至少9個大牌點。如果開叫者再叫 1NT，此後接力方式完全遵循 1♠ – 1NT 的設計（第五章）。其他叫牌都是自然的。</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>2♥</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
+          <t>積極應叫</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="inlineStr">
+        <is>
+          <t>見第五章</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>1NT</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>均型牌，9（10）-15個大牌點。</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>2♣</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
           <t>接力扳機</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>見表 10</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>2♥</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>低花中有9張牌（4-5或5-4），至少8個大牌點。</t>
-        </is>
-      </c>
-      <c r="C9" s="15" t="inlineStr">
-        <is>
-          <t>2♠</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>接力扳機</t>
-        </is>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>見表 11</t>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>見表 6、7</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
+          <t>2♣</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>至少5張♣和9個大牌點。但5332牌型帶一低花套通常被認為是均型牌。</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>2♦</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>接力扳機</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>見表 8、9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>2♦</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>至少5張♦和9個大牌點，其餘同 2♣。</t>
+        </is>
+      </c>
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>2♥</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>接力扳機</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>見表 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>2♥</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>低花中有9張牌（4-5或5-4），至少9個大牌點。</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
           <t>2♠</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
-        <is>
-          <t>均型牌，有兩個4張套，至少15個大牌點。</t>
-        </is>
-      </c>
-      <c r="C10" s="12" t="inlineStr">
-        <is>
-          <t>2NT</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D12" s="11" t="inlineStr">
         <is>
           <t>接力扳機</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>見表 12</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>2NT</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>均型牌，有一個4張套或者一個5張低花套，至少15個大牌點。</t>
-        </is>
-      </c>
-      <c r="C11" s="15" t="inlineStr">
-        <is>
-          <t>3♣</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>接力扳機</t>
-        </is>
-      </c>
-      <c r="E11" s="14" t="inlineStr">
-        <is>
-          <t>見表 13</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="inlineStr">
-        <is>
-          <t>▸ 3♣</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>4441牌型，有一門黑花色是單張，8-12個大牌點。</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>3♦</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>接力（Sidestep原則）</t>
-        </is>
-      </c>
-      <c r="E12" s="17" t="inlineStr">
-        <is>
-          <t>以下 2 列為子接力</t>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>見表 11</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
+          <t>2♠</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>【第十一章改動1】4-4-4-1牌型，有一個**黑花色**單張，13個以上大牌點。（原含義「均型牌、兩個4張套、16+點」已併入 1♥ 應叫）</t>
+        </is>
+      </c>
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>2NT</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>接力扳機</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>原設計見表 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>2NT</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>【第十一章改動1】4-4-4-1牌型，有一個**紅花色**單張，13個以上大牌點。（原含義「均型牌、一個4張套或5張低花套、16+點」已併入 1♥ 應叫）</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>3♣</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>接力扳機</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>原設計見表 13</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>▸ 3♣</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>4441牌型，有一門黑花色是單張，9-13個大牌點。</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>3♦</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>接力（Sidestep原則）</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>以下 2 列為子接力</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
           <t xml:space="preserve">　3♥</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>1-4-4-4分佈</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="D16" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E16" s="17" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♠</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>4-4-4-1分佈</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="D17" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E17" s="17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>▸ 3♦</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>4441牌型，有一門紅花色是單張，8-12個大牌點。</t>
-        </is>
-      </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>4441牌型，有一門紅花色是單張，9-13個大牌點。</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="D18" s="14" t="inlineStr">
         <is>
           <t>接力</t>
         </is>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>以下 2 列為子接力</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♠</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>4-1-4-4分佈</t>
         </is>
       </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="D19" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E19" s="17" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3NT</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>4-4-1-4分佈</t>
         </is>
       </c>
-      <c r="C17" s="21" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="10" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E20" s="17" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="B18" s="11" t="inlineStr">
-        <is>
-          <t>有一門堅固7張套花色。3NT 或加叫應叫者的套進局都表示開叫者是低限；3♠ 再叫是詢問應叫者的堅固套；4♣ 要求應叫者開始扣叫。</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>一個堅固的7張套花色，**邊花沒有牌力**。3NT 或加叫應叫者的套進局都表示開叫者是低限；3♠ 再叫是詢問應叫者的堅固套；4♣ 要求應叫者開始扣叫。</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>3♠／4♣</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>詢問／要求扣叫</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>開叫者只要在其餘三門都有大牌就能推出是哪門</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>3♠／3NT／4♣／4♦</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>4441牌型，比應叫花色高一級的花色是單張，至少12個大牌點。</t>
-        </is>
-      </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>【改動1】加註「邊花沒有牌力」以與 3♠ 區別</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>3♠</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>【第十一章改動1】隨你定！（例如可以是一個堅固的7張套花色，**邊花還有牌力**）</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>接下來是 CRASH</t>
-        </is>
-      </c>
-      <c r="E19" s="14" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>由搭檔自訂</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>取代原本的 3♠／3NT／4♣／4♦（4441，13+點）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>4♥／4♠</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>8或7張半堅固套，不超過一個失張。旁門沒有力量。</t>
         </is>
       </c>
-      <c r="C20" s="12" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>止叫</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="E23" s="20" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>藍底列為上層應叫，黃底列為其子接力答叫。</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>【第十一章改動1】1♥ 應叫被賦予雙重含義（5張以上♥／15+均型），開叫者用 1♠ 接力區分，1NT 則顯示♠套。這騰出了 2♠、2NT 兩個叫品改給 13+ 點的 4441，原本的 3♠／3NT／4♣／4♦（4441、13+）一併取代。</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>書中未列出新的 2♠／2NT（4441、12+）之後的答叫階梯——可比照 3♣／3♦（4441、8-12）的子接力，但原書未明文，本表不代為補寫。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="5">
+    <mergeCell ref="A26:E26"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A25:E25"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2924,7 +3444,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – 1♦ ； ？　（除 1♥ 外所有叫品都顯示 16-19 個大牌點）</t>
+          <t>1♣ – 1♦ ； ？　（除 1♥ 外所有叫品都顯示 15-18 個大牌點）</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3473,7 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>至少20個大牌點，任意牌型。</t>
+          <t>至少19個大牌點，任意牌型。</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -2963,17 +3483,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>1♠</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>通常5張以上♠，但有時拿著4張♠+5張低花也可以先叫 1♠。</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr"/>
+      <c r="C5" s="21" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
@@ -2983,23 +3503,23 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>無局時16-19點，有局時17-19點。後續叫牌同第三、四家開叫的 1NT（第六章）。</t>
+          <t>無局時15-18點，有局時16-18點。後續叫牌同第三、四家開叫的 1NT（第六章）。</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2♣／2♦</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>至少5張套，後續叫牌是自然的。但在 2♣ 後我們也用 2♦ 約定叫詢問開叫者有無邊花（2NT 答叫顯示還有一個♦套）。開叫者跳叫到三階邊花套承諾高限（18-19點）。</t>
-        </is>
-      </c>
-      <c r="C7" s="15" t="inlineStr"/>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>至少5張套，後續叫牌是自然的。但在 2♣ 後我們也用 2♦ 約定叫詢問開叫者有無邊花（2NT 答叫顯示還有一個♦套）。開叫者跳叫到三階邊花套承諾高限（17-18點）。</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
@@ -3015,73 +3535,73 @@
       <c r="C8" s="12" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="13" t="inlineStr">
         <is>
           <t>▸ 2♠</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>轉移到 2NT，然後：</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="15" t="inlineStr">
         <is>
           <t>以下 3 列為轉移後的再叫</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♣</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>6張以上♣ + 4張♥</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr"/>
+      <c r="C10" s="18" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♦</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>6張以上♦ + 4張♥</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr"/>
+      <c r="C11" s="18" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♥</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>6張以上♥ + 4張♠</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr"/>
+      <c r="C12" s="18" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2NT</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>5440牌型，5張套是♥。在 2NT 之後，3♣ 進一步詢問分佈（但不逼叫），開叫者遵循 Splinter-relay 的原則顯示缺門。</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr"/>
+      <c r="C13" s="21" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -3097,17 +3617,17 @@
       <c r="C14" s="12" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>5張以上♦ + 5張♥</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr"/>
+      <c r="C15" s="21" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -3123,17 +3643,17 @@
       <c r="C16" s="12" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>♠單套牌，9贏墩。</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr"/>
+      <c r="C17" s="21" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
@@ -3191,7 +3711,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – 1♦ ； 1♥ – ？　（1♥ = 至少20個大牌點。除 1♠ 外所有叫品都是進局逼叫，顯示 5-8 點）</t>
+          <t>1♣ – 1♦ ； 1♥ – ？　（1♥ = 至少19個大牌點。除 1♠ 外所有叫品都是進局逼叫，顯示 6-9 點）</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3750,7 @@
       </c>
       <c r="B4" s="11" t="inlineStr">
         <is>
-          <t>0-4（5）個大牌點，任意牌型。開叫者此後：1NT = 20-21點；2NT = 22-23點且均型；2♣ = 23點以上的新約定叫，逼叫一輪（對此 2♦ 是三度示弱 0-2 點，其他叫牌自然，表示 3-4 點）。</t>
+          <t>0-5（6）個大牌點，任意牌型。開叫者此後：1NT = 19-20點；2NT = 21-22點且均型；2♣ = 22點以上的新約定叫，逼叫一輪（對此 2♦ 是三度示弱 0-3 點，其他叫牌自然，表示 4-5 點）。</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
@@ -3250,27 +3770,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>1NT</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>至少有一高花5張套。在 1NT 後，2♣ 是一種新的接力：2♦ 表示♠套（2♥ 再次接力，見表 5）；2♥ 及更高的應叫表示♥套，接下來參考 1♥–1NT–2♣–2♦ 後的叫牌（第五章）。</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>2♣</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D5" s="20" t="inlineStr">
         <is>
           <t>新的接力</t>
         </is>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="20" t="inlineStr">
         <is>
           <t>例外：3♣／3♦ 顯示該低花是4或5張套，其後用 '54Pick-up（5-5、5422、5413、5431）</t>
         </is>
@@ -3300,127 +3820,127 @@
       <c r="E6" s="11" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>2♦</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>5張以上♦。後續叫牌同 1♣ – 2♦ – 2♥。</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="20" t="inlineStr">
         <is>
           <t>見表 10</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>▸ 2♥</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>5張以上♣ + 4張邊花套。</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="15" t="inlineStr">
         <is>
           <t>2♠</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Sidestep 接力</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>以下 3 列為子接力</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　2NT</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>4張以上♦</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="17" t="inlineStr">
         <is>
           <t>'54Pick-up　＊</t>
         </is>
       </c>
-      <c r="E9" s="20" t="inlineStr"/>
+      <c r="E9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♣</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>4張以上♥</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>'54Pick-up　＊</t>
         </is>
       </c>
-      <c r="E10" s="20" t="inlineStr"/>
+      <c r="E10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♦</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>4張以上♠</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="17" t="inlineStr">
         <is>
           <t>'54Pick-up　＊</t>
         </is>
       </c>
-      <c r="E11" s="20" t="inlineStr"/>
+      <c r="E11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -3446,27 +3966,27 @@
       <c r="E12" s="11" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>2NT</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>4441牌型，單張花色不明。</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
         <is>
           <t>Splinter</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr"/>
+      <c r="E13" s="20" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
@@ -3492,32 +4012,32 @@
       <c r="E14" s="11" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>顯示5張以上♦ + 5張♣。</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr"/>
+      <c r="E15" s="20" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>【1♠ 示弱線之後的 NT 點力階梯】　1♣–1♦ = 0-7點　→　1♥–1♠ = 0-4點　→　2♣–2♦ = 0-2點　→　2NT = 24-25點／3NT = 26-27點／4NT = 28-30點／5NT = 30-32點（此處數的是聯手大牌點，與接力級數無關）</t>
+          <t>【1♠ 示弱線之後的 NT 點力階梯】　1♣–1♦ = 0-8點　→　1♥–1♠ = 0-5點　→　2♣–2♦ = 0-3點　→　2NT = 24-25點／3NT = 26-27點／4NT = 28-30點／5NT = 30-32點（此處數的是聯手大牌點，與接力級數無關）</t>
         </is>
       </c>
       <c r="B16" s="23" t="n"/>
@@ -3584,7 +4104,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>1♦ = 0-7點　｜　1♥ = 至少20點　｜　1NT = 某一門高花為至少5張套　｜　2♦ = 至少5張♠，4-7點</t>
+          <t>1♦ = 0-8點　｜　1♥ = 至少19點　｜　1NT = 某一門高花為至少5張套　｜　2♦ = 至少5張♠，5-8點</t>
         </is>
       </c>
     </row>
@@ -3639,169 +4159,169 @@
       <c r="E5" s="11" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>▸ 2NT</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>有一♥邊花套，或為均型牌。</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="15" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>'54Pick-up</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="14" t="inlineStr">
         <is>
           <t>以下 6 列為子接力</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♦</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>5332牌型</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr"/>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♥</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>6張以上♠ + 4張♥</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="E8" s="20" t="inlineStr"/>
+      <c r="E8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♠</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>5張♠ + 5張♥</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3NT</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>5-4-2-2</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　4♣</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>5-4-1-3</t>
         </is>
       </c>
-      <c r="C11" s="21" t="inlineStr">
+      <c r="C11" s="18" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="inlineStr"/>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E11" s="17" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　4♦</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>5-4-3-1</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>4NT</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="inlineStr"/>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -3827,27 +4347,27 @@
       <c r="E13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>4張以上♦</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>'54Pick-up　＊</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr"/>
+      <c r="E14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -3873,27 +4393,27 @@
       <c r="E15" s="11" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>6張以上♠ + 5張♦</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Sidestep　＊</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -3919,27 +4439,27 @@
       <c r="E17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>6張♠ + 6張♣</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>Sidestep　＊</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr"/>
+      <c r="E18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -4008,14 +4528,14 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – 1NT ； 2♣ – ？　（所有除了 2♦ 和 3NT 以外的應叫都顯示 8-11 個大牌點）</t>
+          <t>1♣ – 1NT ； 2♣ – ？　（所有除了 2♦ 和 3NT 以外的應叫都顯示 9-12 個大牌點）</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>1NT = 均型牌，8（9）-14個大牌點。</t>
+          <t>1NT = 均型牌，9（10）-15個大牌點。</t>
         </is>
       </c>
     </row>
@@ -4054,7 +4574,7 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>12-14大牌點</t>
+          <t>13-15大牌點</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
@@ -4074,27 +4594,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>2♥</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>4張♥，9-11大牌點</t>
-        </is>
-      </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>4張♥，10-12大牌點</t>
+        </is>
+      </c>
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>2♠</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>接力</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr"/>
+      <c r="E6" s="20" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
@@ -4104,7 +4624,7 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>4張♠，9-11大牌點</t>
+          <t>4張♠，10-12大牌點</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
@@ -4120,27 +4640,27 @@
       <c r="E7" s="11" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>2NT</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>沒有4張高花或5張低花，9-11大牌點</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>沒有4張高花或5張低花，10-12大牌點</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>接力</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr"/>
+      <c r="E8" s="20" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="10" t="inlineStr">
@@ -4150,7 +4670,7 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>5332牌型，5張套是♣，9-11大牌點</t>
+          <t>5332牌型，5張套是♣，10-12大牌點</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
@@ -4166,27 +4686,27 @@
       <c r="E9" s="11" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>5332牌型，5張套是♦，9-11大牌點</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>5332牌型，5張套是♦，10-12大牌點</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>Splinter接力</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr"/>
+      <c r="E10" s="20" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
@@ -4196,7 +4716,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>2-2-4-5分佈，9-11大牌點</t>
+          <t>2-2-4-5分佈，10-12大牌點</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -4212,27 +4732,27 @@
       <c r="E11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>2-2-5-4分佈，9-11大牌點</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>2-2-5-4分佈，10-12大牌點</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -4242,7 +4762,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>3-3-3-4分佈，12-14大牌點</t>
+          <t>3-3-3-4分佈，13-15大牌點</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -4267,7 +4787,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>記住：所有 5-3-3-2 牌型、5張套為低花的牌，不管大牌點如何分佈都要應叫 1NT；但持 12-14 點和 5-4 型必須應叫 2 階低花。</t>
+          <t>記住：所有 5-3-3-2 牌型、5張套為低花的牌，不管大牌點如何分佈都要應叫 1NT；但持 13-15 點和 5-4 型必須應叫 2 階低花。</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4836,7 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>2♦ = 12-14大牌點。</t>
+          <t>2♦ = 13-15大牌點。</t>
         </is>
       </c>
     </row>
@@ -4348,288 +4868,288 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>▸ 2♠</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>4張♠，但不否認4張♥</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="15" t="inlineStr">
         <is>
           <t>2NT</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
         <is>
           <t>一種新的接力</t>
         </is>
       </c>
-      <c r="E5" s="17" t="inlineStr">
+      <c r="E5" s="14" t="inlineStr">
         <is>
           <t>以下 5 列為子接力</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♣</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>4張♣ + 4張♠</t>
         </is>
       </c>
-      <c r="C6" s="21" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr"/>
+      <c r="E6" s="17" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♦</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>4張♦ + 4張♠</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="E7" s="20" t="inlineStr"/>
+      <c r="E7" s="17" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♥</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>4-4-2-3</t>
         </is>
       </c>
-      <c r="C8" s="21" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E8" s="20" t="inlineStr"/>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♠</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>4-4-3-2</t>
         </is>
       </c>
-      <c r="C9" s="21" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="inlineStr"/>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E9" s="17" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3NT</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>4-3-3-3</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="inlineStr"/>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="16" t="inlineStr">
+      <c r="A11" s="13" t="inlineStr">
         <is>
           <t>▸ 2NT</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>4張♥</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="15" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>一種新的接力</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>以下 4 列為子接力</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♦</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>4張♦ + 4張♥</t>
         </is>
       </c>
-      <c r="C12" s="21" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
-      <c r="E12" s="20" t="inlineStr"/>
+      <c r="E12" s="17" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♥</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2-4-3-4</t>
         </is>
       </c>
-      <c r="C13" s="21" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="inlineStr"/>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E13" s="17" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3♠</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>3-4-2-4</t>
         </is>
       </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="inlineStr"/>
+      <c r="D14" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E14" s="17" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">　3NT</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>3-4-3-3</t>
         </is>
       </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="inlineStr"/>
+      <c r="D15" s="17" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E15" s="17" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>5332牌型，5張♣</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>Splinter接力</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr"/>
+      <c r="E16" s="20" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
@@ -4655,27 +5175,27 @@
       <c r="E17" s="11" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>2-3-4-4</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E18" s="14" t="inlineStr"/>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
@@ -4701,27 +5221,27 @@
       <c r="E19" s="11" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="13" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>3-3-4-3</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr"/>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4767,7 +5287,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>1♣ – 2♣ ； 2♦ – ？　（2♣ = 5張♣，8+大牌點。應叫者有 11 種可能的再叫）</t>
+          <t>1♣ – 2♣ ； 2♦ – ？　（2♣ = 5張♣，9+大牌點。應叫者有 11 種可能的再叫）</t>
         </is>
       </c>
     </row>
@@ -4833,27 +5353,27 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>B　2♠</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>4張♠</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>2NT</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>'54Pick-up</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="20" t="inlineStr">
         <is>
           <t>見表 9</t>
         </is>
@@ -4887,27 +5407,27 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>D　3♣</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>6張以上♣套，沒有其他邊花</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>接力</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="20" t="inlineStr">
         <is>
           <t>見表 9</t>
         </is>
@@ -4941,27 +5461,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>F　3♥</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>7張♣，8-11大牌點</t>
-        </is>
-      </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>7張♣，9-12大牌點</t>
+        </is>
+      </c>
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>接力</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="20" t="inlineStr">
         <is>
           <t>見表 9</t>
         </is>
@@ -4975,7 +5495,7 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>7321牌型，12+大牌點</t>
+          <t>7321牌型，13+大牌點</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
@@ -4991,27 +5511,27 @@
       <c r="E11" s="11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>2-2-2-7，12+大牌點</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>2-2-2-7，13+大牌點</t>
+        </is>
+      </c>
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E12" s="14" t="inlineStr"/>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -5021,7 +5541,7 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>3-3-0-7，12+大牌點</t>
+          <t>3-3-0-7，13+大牌點</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
@@ -5037,27 +5557,27 @@
       <c r="E13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>3-0-3-7，12+大牌點</t>
-        </is>
-      </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>3-0-3-7，13+大牌點</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
-        <is>
-          <t>CRASH</t>
-        </is>
-      </c>
-      <c r="E14" s="14" t="inlineStr"/>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>CRASH</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -5067,7 +5587,7 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>0-3-3-7，12+大牌點</t>
+          <t>0-3-3-7，13+大牌點</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
@@ -5164,1044 +5684,1044 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>1♣–2♣；2♦–2♥；2♠–？
 2♥ = 4張♥
-高於 3♣ 的應叫都表示 12+ 點</t>
-        </is>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
+高於 3♣ 的應叫都表示 13+ 點</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>2NT</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
-        <is>
-          <t>8-11大牌點</t>
-        </is>
-      </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>9-12大牌點</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>'54Pick-up　＊</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr"/>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>6張以上♣ + 4張♥，12+</t>
         </is>
       </c>
-      <c r="E6" s="15" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr"/>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
         <is>
           <t>2-4-2-5，12+</t>
         </is>
       </c>
-      <c r="E7" s="15" t="inlineStr">
+      <c r="E7" s="21" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr"/>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr"/>
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="20" t="inlineStr">
         <is>
           <t>1-4-3-5，12+</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E8" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr">
         <is>
           <t>3-4-1-5，12+</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr"/>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>6張以上♣ + 5張♥，12+</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E10" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr"/>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
         <is>
           <t>0-4-4-5，12+</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E11" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr"/>
-      <c r="C12" s="13" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr"/>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
         <is>
           <t>4-4-0-5，12+</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="21" t="inlineStr">
         <is>
           <t>4NT</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>1♣–2♣；2♦–2♠；2NT–？
 2♠ = 4張♠
-高於 3♦ 的應叫都表示 12+ 點</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+高於 3♦ 的應叫都表示 13+ 點</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>3♣</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>8-11大牌點</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="inlineStr">
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>9-12大牌點</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="F13" s="20" t="inlineStr">
+      <c r="F13" s="17" t="inlineStr">
         <is>
           <t>'54Pick-up　＊</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="13" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr"/>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>6張以上♣ + 4張♠，12+</t>
         </is>
       </c>
-      <c r="E14" s="15" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr"/>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
         <is>
           <t>4-2-2-5，12+</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="13" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr"/>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr"/>
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>4-1-3-5，12+</t>
         </is>
       </c>
-      <c r="E16" s="15" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr"/>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr"/>
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>4-3-1-5，12+</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr"/>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr"/>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="20" t="inlineStr">
         <is>
           <t>6張以上♣ + 5張♠，12+</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr"/>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D19" s="14" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>4-0-4-5，12+</t>
         </is>
       </c>
-      <c r="E19" s="15" t="inlineStr">
+      <c r="E19" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="17" t="inlineStr">
         <is>
           <t>1♣–2♣；2♦–2NT；3♣–？
 2NT = 至少5張♣ + 5張♦
-高於 3♥ 的應叫都表示 12+ 點</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
+高於 3♥ 的應叫都表示 13+ 點</t>
+        </is>
+      </c>
+      <c r="C20" s="16" t="inlineStr">
         <is>
           <t>3♦</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>8-11大牌點</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="inlineStr">
+      <c r="D20" s="17" t="inlineStr">
+        <is>
+          <t>9-12大牌點</t>
+        </is>
+      </c>
+      <c r="E20" s="18" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="F20" s="20" t="inlineStr">
+      <c r="F20" s="17" t="inlineStr">
         <is>
           <t>接力　＊</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="13" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B21" s="14" t="inlineStr"/>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr"/>
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D21" s="14" t="inlineStr">
+      <c r="D21" s="20" t="inlineStr">
         <is>
           <t>5張♣ + 5張♦，12+</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E21" s="21" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B22" s="14" t="inlineStr"/>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr"/>
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D22" s="14" t="inlineStr">
+      <c r="D22" s="20" t="inlineStr">
         <is>
           <t>6張以上♣ + 5張♦，12+</t>
         </is>
       </c>
-      <c r="E22" s="15" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="13" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B23" s="14" t="inlineStr"/>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="D23" s="14" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
         <is>
           <t>5張♣ + 6張以上♦，12+</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
+      <c r="E23" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="13" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr"/>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr"/>
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D24" s="14" t="inlineStr">
+      <c r="D24" s="20" t="inlineStr">
         <is>
           <t>6張♣ + 6張♦，12+</t>
         </is>
       </c>
-      <c r="E24" s="15" t="inlineStr">
+      <c r="E24" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>1♣–2♣；2♦–3♣；3♦–？
 3♣ = 至少6張♣，無邊花套
-高於 3♠ 的應叫都表示 12+ 點</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
+高於 3♠ 的應叫都表示 13+ 點</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
         <is>
           <t>3♥</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>8-11大牌點</t>
-        </is>
-      </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>9-12大牌點</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="F25" s="20" t="inlineStr">
+      <c r="F25" s="17" t="inlineStr">
         <is>
           <t>接力　＊</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr"/>
-      <c r="C26" s="13" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr"/>
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D26" s="14" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>6322牌型，12+</t>
         </is>
       </c>
-      <c r="E26" s="15" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F26" s="14" t="inlineStr">
+      <c r="F26" s="20" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr"/>
-      <c r="C27" s="13" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>3-3-1-6，12+</t>
         </is>
       </c>
-      <c r="E27" s="15" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F27" s="14" t="inlineStr">
+      <c r="F27" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr"/>
-      <c r="C28" s="13" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr"/>
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D28" s="14" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
         <is>
           <t>3-1-3-6，12+</t>
         </is>
       </c>
-      <c r="E28" s="15" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F28" s="14" t="inlineStr">
+      <c r="F28" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr"/>
-      <c r="C29" s="13" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr"/>
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D29" s="14" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
         <is>
           <t>1-3-3-6，12+</t>
         </is>
       </c>
-      <c r="E29" s="15" t="inlineStr">
+      <c r="E29" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="F29" s="14" t="inlineStr">
+      <c r="F29" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="19" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>1♣–2♣；2♦–3♦；3♥–？
 3♦ = 4張♦ + 至少6張♣
-高於 3NT 的應叫都表示 12+ 點</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
+高於 3NT 的應叫都表示 13+ 點</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
         <is>
           <t>3♠</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>8-11大牌點</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>9-12大牌點</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F30" s="20" t="inlineStr">
+      <c r="F30" s="17" t="inlineStr">
         <is>
           <t>Sidestep</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr"/>
-      <c r="C31" s="13" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr"/>
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="D31" s="14" t="inlineStr">
+      <c r="D31" s="20" t="inlineStr">
         <is>
           <t>1-2-4-6，12+</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E31" s="21" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F31" s="14" t="inlineStr">
+      <c r="F31" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="13" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr"/>
-      <c r="C32" s="13" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr"/>
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D32" s="14" t="inlineStr">
+      <c r="D32" s="20" t="inlineStr">
         <is>
           <t>2-1-4-6，12+</t>
         </is>
       </c>
-      <c r="E32" s="15" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F32" s="14" t="inlineStr">
+      <c r="F32" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="13" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr"/>
-      <c r="C33" s="13" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr"/>
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D33" s="14" t="inlineStr">
+      <c r="D33" s="20" t="inlineStr">
         <is>
           <t>0-3-4-6，12+</t>
         </is>
       </c>
-      <c r="E33" s="15" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="F33" s="14" t="inlineStr">
+      <c r="F33" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="13" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr"/>
-      <c r="C34" s="13" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr"/>
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="D34" s="14" t="inlineStr">
+      <c r="D34" s="20" t="inlineStr">
         <is>
           <t>3-0-4-6，12+</t>
         </is>
       </c>
-      <c r="E34" s="15" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>4♠</t>
         </is>
       </c>
-      <c r="F34" s="14" t="inlineStr">
+      <c r="F34" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr"/>
-      <c r="C35" s="13" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr"/>
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>4♠</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
+      <c r="D35" s="20" t="inlineStr">
         <is>
           <t>1-1-4-7，12+</t>
         </is>
       </c>
-      <c r="E35" s="15" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>4NT</t>
         </is>
       </c>
-      <c r="F35" s="14" t="inlineStr">
+      <c r="F35" s="20" t="inlineStr">
         <is>
           <t>黑木</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="17" t="inlineStr">
         <is>
           <t>1♣–2♣；2♦–3♥；3♠–？
-3♥ = 7張♣，8-11大牌點
+3♥ = 7張♣，9-12大牌點
 應叫者有 5 種可能的再叫</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="16" t="inlineStr">
         <is>
           <t>3NT</t>
         </is>
       </c>
-      <c r="D36" s="20" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>2-2-2-7</t>
         </is>
       </c>
-      <c r="E36" s="21" t="inlineStr">
+      <c r="E36" s="18" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="F36" s="20" t="inlineStr">
+      <c r="F36" s="17" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="13" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr"/>
-      <c r="C37" s="13" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>4♣</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
         <is>
           <t>7321牌型</t>
         </is>
       </c>
-      <c r="E37" s="15" t="inlineStr">
+      <c r="E37" s="21" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="F37" s="14" t="inlineStr">
+      <c r="F37" s="20" t="inlineStr">
         <is>
           <t>Splinter接力</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr"/>
-      <c r="C38" s="13" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr"/>
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>4♦</t>
         </is>
       </c>
-      <c r="D38" s="14" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
         <is>
           <t>3-3-0-7</t>
         </is>
       </c>
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E38" s="21" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="F38" s="14" t="inlineStr">
+      <c r="F38" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="13" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr"/>
-      <c r="C39" s="13" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr"/>
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>4♥</t>
         </is>
       </c>
-      <c r="D39" s="14" t="inlineStr">
+      <c r="D39" s="20" t="inlineStr">
         <is>
           <t>3-0-3-7</t>
         </is>
       </c>
-      <c r="E39" s="15" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>4♠</t>
         </is>
       </c>
-      <c r="F39" s="14" t="inlineStr">
+      <c r="F39" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr"/>
-      <c r="C40" s="13" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr"/>
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>4♠</t>
         </is>
       </c>
-      <c r="D40" s="14" t="inlineStr">
+      <c r="D40" s="20" t="inlineStr">
         <is>
           <t>0-3-3-7</t>
         </is>
       </c>
-      <c r="E40" s="15" t="inlineStr">
+      <c r="E40" s="21" t="inlineStr">
         <is>
           <t>4NT</t>
         </is>
       </c>
-      <c r="F40" s="14" t="inlineStr">
+      <c r="F40" s="20" t="inlineStr">
         <is>
           <t>CRASH</t>
         </is>
@@ -6210,7 +6730,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>＊ 後續答叫的設計和該分支的階梯一模一樣，只要多加一級即可（第一級用來表示 8-11 點的低限，其餘整體順延）。</t>
+          <t>＊ 後續答叫的設計和該分支的階梯一模一樣，只要多加一級即可（第一級用來表示 9-12 點的低限，其餘整體順延）。</t>
         </is>
       </c>
     </row>

--- a/原始資料/一梅花開叫.xlsx
+++ b/原始資料/一梅花開叫.xlsx
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>無局時15-18點，有局時16-18點。後續叫牌同第三、四家開叫的 1NT（第六章）。</t>
+          <t>無局時15-18點，有局時16-18點。後續叫牌同第六章 1NT 開叫後的設計（此處點力另計——家規下第六章的 1NT 開叫一律 10-12 點，原書的「第三、四家 13-15」已不存在）。</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr"/>

--- a/原始資料/一梅花開叫.xlsx
+++ b/原始資料/一梅花開叫.xlsx
@@ -3503,7 +3503,7 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>無局時15-18點，有局時16-18點。後續叫牌同第六章 1NT 開叫後的設計（此處點力另計——家規下第六章的 1NT 開叫一律 10-12 點，原書的「第三、四家 13-15」已不存在）。</t>
+          <t>15-18點。後續叫牌同第六章 1NT 開叫後的設計（此處點力另計——家規下第六章的 1NT 開叫一律 10-12 點，原書的「第三、四家 13-15」已不存在）。</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr"/>
